--- a/data/trans_dic/P6905-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 25,63</t>
+          <t>7,31; 25,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 36,32</t>
+          <t>16,97; 37,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 37,83</t>
+          <t>13,6; 37,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 30,46</t>
+          <t>6,69; 30,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 43,37</t>
+          <t>12,31; 43,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 67,67</t>
+          <t>30,99; 67,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,17; 63,65</t>
+          <t>27,02; 61,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 38,9</t>
+          <t>18,73; 40,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,69; 26,77</t>
+          <t>11,68; 26,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,53; 43,78</t>
+          <t>24,9; 43,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,98; 42,33</t>
+          <t>21,44; 42,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 30,04</t>
+          <t>14,63; 31,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 37,54</t>
+          <t>21,91; 38,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 33,48</t>
+          <t>15,85; 34,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 31,37</t>
+          <t>12,93; 30,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 33,62</t>
+          <t>14,73; 33,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,41; 53,42</t>
+          <t>27,34; 54,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 61,68</t>
+          <t>36,47; 61,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,27; 46,55</t>
+          <t>20,05; 44,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 43,65</t>
+          <t>26,38; 43,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 39,51</t>
+          <t>25,37; 39,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,05; 41,83</t>
+          <t>26,36; 42,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 34,12</t>
+          <t>19,01; 34,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,74; 35,22</t>
+          <t>22,5; 34,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,46; 40,55</t>
+          <t>20,45; 40,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,45; 42,76</t>
+          <t>20,53; 41,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,53; 39,98</t>
+          <t>22,6; 40,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 31,74</t>
+          <t>10,08; 31,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 61,05</t>
+          <t>31,68; 61,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,27; 45,54</t>
+          <t>20,7; 45,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,22; 54,63</t>
+          <t>31,32; 55,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 46,56</t>
+          <t>10,78; 47,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,51; 43,57</t>
+          <t>27,72; 44,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,83; 40,16</t>
+          <t>23,05; 40,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,02; 42,37</t>
+          <t>28,0; 42,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 34,99</t>
+          <t>11,79; 35,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,54; 47,94</t>
+          <t>31,26; 47,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 33,7</t>
+          <t>15,2; 34,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 42,47</t>
+          <t>22,4; 42,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 40,29</t>
+          <t>20,81; 41,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,17; 55,15</t>
+          <t>34,76; 54,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,19; 49,98</t>
+          <t>24,7; 50,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,42; 59,84</t>
+          <t>33,8; 60,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,85; 47,09</t>
+          <t>26,98; 47,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,51; 47,7</t>
+          <t>34,38; 47,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,92; 37,36</t>
+          <t>21,48; 37,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 46,29</t>
+          <t>30,38; 46,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,46; 40,61</t>
+          <t>26,12; 39,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,47; 34,65</t>
+          <t>26,21; 35,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,41; 31,37</t>
+          <t>21,42; 30,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,91; 32,71</t>
+          <t>22,48; 32,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,89; 29,25</t>
+          <t>18,32; 28,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,05; 47,36</t>
+          <t>34,53; 47,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,47; 48,33</t>
+          <t>33,72; 48,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,37</t>
+          <t>34,46; 48,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,67; 38,34</t>
+          <t>23,43; 38,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,19; 37,43</t>
+          <t>29,6; 37,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,81; 36,27</t>
+          <t>28,28; 35,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,42</t>
+          <t>28,62; 36,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,49</t>
+          <t>23,19; 31,74</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores de cabeza (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6074; 20334</t>
+          <t>5798; 20270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13016; 27810</t>
+          <t>12996; 28453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7320; 20681</t>
+          <t>7434; 20649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4991; 21691</t>
+          <t>4765; 21737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3979; 13982</t>
+          <t>3967; 14128</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11096; 23184</t>
+          <t>10617; 22959</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8128; 19042</t>
+          <t>8083; 18537</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10825; 21273</t>
+          <t>10243; 22099</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13043; 29866</t>
+          <t>13028; 29972</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27190; 48522</t>
+          <t>27598; 48155</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18592; 35803</t>
+          <t>18138; 35535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18559; 37815</t>
+          <t>18416; 39071</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31102; 54807</t>
+          <t>31980; 56318</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13816; 30394</t>
+          <t>14386; 31595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12426; 30423</t>
+          <t>12536; 29745</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15491; 37644</t>
+          <t>16495; 37309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14471; 28206</t>
+          <t>14433; 28649</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23636; 39168</t>
+          <t>23160; 38801</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11815; 25860</t>
+          <t>11138; 24701</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26395; 43094</t>
+          <t>26043; 42461</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52376; 78533</t>
+          <t>50423; 77908</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40189; 64532</t>
+          <t>40667; 65278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27909; 52037</t>
+          <t>29002; 52451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47909; 74218</t>
+          <t>47412; 72933</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23589; 44586</t>
+          <t>22484; 44019</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16269; 34015</t>
+          <t>16330; 33351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24765; 43954</t>
+          <t>24851; 44399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5434; 17547</t>
+          <t>5571; 17491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14724; 28406</t>
+          <t>14740; 28650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10738; 24125</t>
+          <t>10969; 24188</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20214; 35373</t>
+          <t>20277; 36098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9901; 45123</t>
+          <t>10447; 45829</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43047; 68172</t>
+          <t>43376; 69307</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30261; 53222</t>
+          <t>30555; 53088</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48951; 74009</t>
+          <t>48906; 74240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18377; 53245</t>
+          <t>17940; 54710</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41856; 65707</t>
+          <t>42843; 65697</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11439; 26432</t>
+          <t>11921; 27272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19155; 37546</t>
+          <t>19800; 37347</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20812; 40702</t>
+          <t>21025; 42073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30255; 48839</t>
+          <t>30776; 48532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15503; 32033</t>
+          <t>15833; 32614</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22086; 39541</t>
+          <t>22336; 40024</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27898; 48925</t>
+          <t>28035; 49393</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77862; 107605</t>
+          <t>77560; 107628</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31241; 53246</t>
+          <t>30616; 53072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47004; 71511</t>
+          <t>46933; 71944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54231; 83214</t>
+          <t>53521; 81656</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>120280; 163652</t>
+          <t>123771; 166150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69651; 102071</t>
+          <t>69688; 100601</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80193; 114490</t>
+          <t>78681; 112585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60738; 99292</t>
+          <t>62196; 97889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77154; 104241</t>
+          <t>76002; 104901</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74043; 103828</t>
+          <t>72440; 103677</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75682; 104613</t>
+          <t>74529; 104549</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>83849; 135810</t>
+          <t>82978; 136476</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>209046; 259159</t>
+          <t>204964; 256786</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150211; 195919</t>
+          <t>152744; 193169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160012; 206249</t>
+          <t>162076; 208156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>160456; 218460</t>
+          <t>160841; 220170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6905-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6905-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 25,55</t>
+          <t>7,63; 24,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 37,15</t>
+          <t>16,49; 38,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 37,77</t>
+          <t>13,21; 37,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 30,52</t>
+          <t>7,54; 31,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 43,82</t>
+          <t>12,29; 44,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,99; 67,01</t>
+          <t>32,09; 67,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,02; 61,97</t>
+          <t>28,12; 65,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 40,41</t>
+          <t>19,01; 40,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,68; 26,86</t>
+          <t>11,01; 26,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 43,44</t>
+          <t>24,85; 43,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,44; 42,01</t>
+          <t>21,47; 41,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 31,03</t>
+          <t>14,73; 32,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,91; 38,58</t>
+          <t>22,92; 38,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 34,8</t>
+          <t>15,35; 33,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 30,67</t>
+          <t>13,46; 31,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,73; 33,32</t>
+          <t>18,78; 38,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,34; 54,26</t>
+          <t>27,05; 53,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,47; 61,11</t>
+          <t>36,51; 61,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 44,47</t>
+          <t>20,98; 46,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 43,01</t>
+          <t>25,99; 41,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 39,19</t>
+          <t>25,74; 39,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,36; 42,31</t>
+          <t>25,59; 41,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,01; 34,39</t>
+          <t>19,33; 33,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 34,61</t>
+          <t>24,6; 37,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,45; 40,04</t>
+          <t>21,9; 41,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 41,92</t>
+          <t>20,62; 43,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,6; 40,39</t>
+          <t>22,41; 40,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 31,64</t>
+          <t>11,67; 35,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,68; 61,57</t>
+          <t>33,24; 61,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 45,66</t>
+          <t>20,07; 45,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,32; 55,75</t>
+          <t>30,67; 54,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 47,29</t>
+          <t>29,63; 51,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 44,29</t>
+          <t>27,21; 43,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 40,06</t>
+          <t>23,29; 40,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,0; 42,5</t>
+          <t>27,68; 42,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,79; 35,95</t>
+          <t>23,57; 39,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 47,94</t>
+          <t>30,6; 47,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 34,77</t>
+          <t>15,19; 34,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,4; 42,24</t>
+          <t>21,22; 42,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 41,64</t>
+          <t>21,34; 39,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 54,81</t>
+          <t>34,02; 55,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,7; 50,88</t>
+          <t>23,1; 48,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,8; 60,57</t>
+          <t>34,23; 59,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,98; 47,54</t>
+          <t>24,16; 40,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,38; 47,71</t>
+          <t>34,4; 47,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 37,24</t>
+          <t>22,33; 37,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,38; 46,57</t>
+          <t>29,81; 46,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,12; 39,85</t>
+          <t>25,3; 37,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,21; 35,18</t>
+          <t>25,66; 34,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 30,92</t>
+          <t>21,08; 31,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,48; 32,17</t>
+          <t>22,77; 32,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,32; 28,83</t>
+          <t>20,28; 30,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,53; 47,66</t>
+          <t>34,12; 48,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,72; 48,26</t>
+          <t>33,92; 47,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,46; 48,34</t>
+          <t>34,96; 48,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,43; 38,53</t>
+          <t>28,95; 38,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 37,08</t>
+          <t>29,8; 37,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,28; 35,76</t>
+          <t>28,2; 36,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,62; 36,76</t>
+          <t>28,67; 36,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,19; 31,74</t>
+          <t>26,02; 32,97</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>30092</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5798; 20270</t>
+          <t>6057; 19736</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12996; 28453</t>
+          <t>12628; 29531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7434; 20649</t>
+          <t>7224; 20293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4765; 21737</t>
+          <t>5658; 23862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3967; 14128</t>
+          <t>3964; 14305</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10617; 22959</t>
+          <t>10996; 23231</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8083; 18537</t>
+          <t>8413; 19566</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10243; 22099</t>
+          <t>11374; 24406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13028; 29972</t>
+          <t>12289; 29568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27598; 48155</t>
+          <t>27541; 48126</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18138; 35535</t>
+          <t>18159; 35430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18416; 39071</t>
+          <t>19869; 43591</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59735</t>
+          <t>72826</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31980; 56318</t>
+          <t>33455; 56448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14386; 31595</t>
+          <t>13932; 30360</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12536; 29745</t>
+          <t>13050; 30631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16495; 37309</t>
+          <t>24971; 50842</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14433; 28649</t>
+          <t>14281; 28069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23160; 38801</t>
+          <t>23186; 39320</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11138; 24701</t>
+          <t>11652; 25774</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26043; 42461</t>
+          <t>27930; 45115</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50423; 77908</t>
+          <t>51170; 77975</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40667; 65278</t>
+          <t>39474; 63915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29002; 52451</t>
+          <t>29491; 51310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47412; 72933</t>
+          <t>59145; 89972</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37934</t>
+          <t>43350</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22484; 44019</t>
+          <t>24080; 45418</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16330; 33351</t>
+          <t>16405; 34761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24851; 44399</t>
+          <t>24634; 44042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5571; 17491</t>
+          <t>8039; 24507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14740; 28650</t>
+          <t>15469; 28732</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10969; 24188</t>
+          <t>10635; 24202</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20277; 36098</t>
+          <t>19858; 35570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10447; 45829</t>
+          <t>20949; 36314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43376; 69307</t>
+          <t>42570; 67680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30555; 53088</t>
+          <t>30874; 53635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48906; 74240</t>
+          <t>48360; 74438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17940; 54710</t>
+          <t>32896; 54713</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67373</t>
+          <t>66829</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42843; 65697</t>
+          <t>41931; 65488</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11921; 27272</t>
+          <t>11913; 26850</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19800; 37347</t>
+          <t>18765; 37160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21025; 42073</t>
+          <t>23065; 43035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30776; 48532</t>
+          <t>30128; 48961</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15833; 32614</t>
+          <t>14809; 31355</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22336; 40024</t>
+          <t>22618; 39588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28035; 49393</t>
+          <t>25931; 43536</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77560; 107628</t>
+          <t>77610; 107705</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30616; 53072</t>
+          <t>31827; 53942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46933; 71944</t>
+          <t>46047; 71796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53521; 81656</t>
+          <t>54500; 80670</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>115965</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>213098</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123771; 166150</t>
+          <t>121184; 162733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69688; 100601</t>
+          <t>68592; 101076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78681; 112585</t>
+          <t>79689; 114016</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62196; 97889</t>
+          <t>78078; 117943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76002; 104901</t>
+          <t>75100; 105759</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72440; 103677</t>
+          <t>72880; 103075</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74529; 104549</t>
+          <t>75610; 105648</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82978; 136476</t>
+          <t>99979; 134155</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>204964; 256786</t>
+          <t>206311; 256365</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>152744; 193169</t>
+          <t>152324; 199139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162076; 208156</t>
+          <t>162334; 206760</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>160841; 220170</t>
+          <t>190026; 240821</t>
         </is>
       </c>
     </row>
